--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104631_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104631_W20.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. BRIMAH</t>
+          <t>J. ROUSSELLE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5513</v>
+        <v>2.4877</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9292</v>
+        <v>3.4691</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6221</v>
+        <v>-0.9814000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.1376</v>
+        <v>1.6151</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.4762</v>
+        <v>-0.6783</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3386</v>
+        <v>2.2933</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.3469</v>
+        <v>4.496</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.0186</v>
+        <v>1.1754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6717</v>
+        <v>3.3206</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-2.8809</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4576</v>
+        <v>-1.8536</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.3331</v>
+        <v>-1.0273</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-2.7316</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>3.8697</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3771</v>
+        <v>-1.5842</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0907</v>
+        <v>-0.4743</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4679</v>
+        <v>-1.1099</v>
       </c>
       <c r="V2" t="n">
-        <v>2.0246</v>
+        <v>1.3187</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1607</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ROUSSELLE</t>
+          <t>A. BRIMAH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1458</v>
+        <v>2.4177</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5512</v>
+        <v>1.8654</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4054</v>
+        <v>0.5523</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6212</v>
+        <v>-1.1307</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6870000000000001</v>
+        <v>-1.4735</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3082</v>
+        <v>0.3428</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5354</v>
+        <v>-0.3574</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1878</v>
+        <v>-1.0277</v>
       </c>
       <c r="L3" t="n">
-        <v>3.3477</v>
+        <v>0.6703</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.9142</v>
+        <v>-0.7733</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8747</v>
+        <v>-0.4458</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0395</v>
+        <v>-0.3275</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.722</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.8562</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9272</v>
+        <v>-0.5214</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4476</v>
+        <v>0.0439</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.4796</v>
+        <v>-0.5653</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3176</v>
+        <v>2.0212</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8678</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>J. PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1862</v>
+        <v>0.4786</v>
       </c>
       <c r="E4" t="n">
-        <v>0.219</v>
+        <v>0.4613</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0328</v>
+        <v>0.0173</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.0267</v>
+        <v>1.9206</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2222</v>
+        <v>-1.1777</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8045</v>
+        <v>3.0983</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.3384</v>
+        <v>3.1256</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.261</v>
+        <v>0.0722</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.07729999999999999</v>
+        <v>3.0534</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6884</v>
+        <v>-1.205</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-1.2499</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7272</v>
+        <v>0.0449</v>
       </c>
       <c r="P4" t="n">
-        <v>0.4537</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9488</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5434</v>
+        <v>-0.2159</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0253</v>
+        <v>-0.1604</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5181</v>
+        <v>-0.0556</v>
       </c>
       <c r="V4" t="n">
-        <v>5.3026</v>
+        <v>-0.3155</v>
       </c>
       <c r="W4" t="n">
-        <v>5.0777</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2249</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. OLUMUYIWA</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0365</v>
+        <v>0.2675</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1642</v>
+        <v>0.4849</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2007</v>
+        <v>-0.2173</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5625</v>
+        <v>-4.0152</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8428</v>
+        <v>-2.2175</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7196</v>
+        <v>-1.7977</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2136</v>
+        <v>-1.3512</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9524</v>
+        <v>-1.269</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2612</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7761</v>
+        <v>-2.664</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7953</v>
+        <v>-0.9485</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-1.7155</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1342</v>
+        <v>0.4553</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.8147</v>
+        <v>-2.5039</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2423</v>
+        <v>-1.4622</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8166</v>
+        <v>-0.7204</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5743</v>
+        <v>-0.7418</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7071</v>
+        <v>5.2896</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2534</v>
+        <v>5.0604</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. PEREZ</t>
+          <t>B. OLUMUYIWA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1009</v>
+        <v>0.0499</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1574</v>
+        <v>0.0958</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2583</v>
+        <v>-0.0459</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9196</v>
+        <v>-1.5435</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1804</v>
+        <v>-0.8334</v>
       </c>
       <c r="I6" t="n">
-        <v>3.1</v>
+        <v>-0.7101</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1395</v>
+        <v>1.2087</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0795</v>
+        <v>0.948</v>
       </c>
       <c r="L6" t="n">
-        <v>3.06</v>
+        <v>0.2607</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2198</v>
+        <v>-2.7522</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2599</v>
+        <v>-1.7814</v>
       </c>
       <c r="O6" t="n">
-        <v>0.04</v>
+        <v>-0.9708</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9073</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.4952</v>
+        <v>-1.8211</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>2.9592</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.2473</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4869</v>
+        <v>-0.5391</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3049</v>
+        <v>0.2919</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3214</v>
+        <v>0.7025</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3214</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9586</v>
+        <v>-0.9977</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8925</v>
+        <v>-0.7524</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06610000000000001</v>
+        <v>-0.2453</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.0148</v>
+        <v>-2.9986</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.8659</v>
+        <v>-1.8532</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1488</v>
+        <v>-1.1454</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6858</v>
+        <v>0.672</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1661</v>
+        <v>0.1584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5135999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7006</v>
+        <v>-3.6706</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.032</v>
+        <v>-2.0116</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="R7" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3076</v>
+        <v>0.2497</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1512</v>
+        <v>0.0112</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4588</v>
+        <v>0.2385</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2121</v>
+        <v>-1.0278</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0273</v>
+        <v>-0.9127999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1848</v>
+        <v>-0.1151</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.954</v>
+        <v>-0.9537</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5511</v>
+        <v>-0.3717</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2782</v>
+        <v>-0.1604</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2728</v>
+        <v>-0.2113</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="9">
@@ -1111,22 +1111,22 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0355</v>
+        <v>-2.0367</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.116</v>
+        <v>-1.1196</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1138,28 +1138,28 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9195</v>
+        <v>-0.9171</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7463</v>
+        <v>-0.7447</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0181</v>
+        <v>0.0185</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0865</v>
+        <v>-2.8222</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7437</v>
+        <v>-2.8074</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3428</v>
+        <v>-0.0148</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.688</v>
+        <v>-4.6954</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.059</v>
+        <v>-4.0637</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6291</v>
+        <v>-0.6317</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8275</v>
+        <v>-0.8698</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2001</v>
+        <v>-2.2245</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3726</v>
+        <v>1.3548</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.8605</v>
+        <v>-3.8257</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.8588</v>
+        <v>-1.8392</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.0017</v>
+        <v>-1.9865</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="R10" t="n">
-        <v>4.083</v>
+        <v>4.0974</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.786</v>
+        <v>-0.5122</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2208</v>
+        <v>-0.2257</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5653</v>
+        <v>-0.2865</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.0195</v>
+        <v>-3.5681</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7048</v>
+        <v>-4.142</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6852</v>
+        <v>0.5739</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.1323</v>
+        <v>-3.1511</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.1829</v>
+        <v>-3.1986</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0506</v>
+        <v>0.0475</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2246</v>
+        <v>0.1719</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.6704</v>
+        <v>-1.7042</v>
       </c>
       <c r="L11" t="n">
-        <v>1.895</v>
+        <v>1.8761</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.3569</v>
+        <v>-3.323</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.5125</v>
+        <v>-1.4945</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8444</v>
+        <v>-1.8285</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.083</v>
+        <v>-4.0974</v>
       </c>
       <c r="R11" t="n">
-        <v>3.8562</v>
+        <v>3.8697</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8211000000000001</v>
+        <v>-0.3472</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0071</v>
+        <v>-0.3743</v>
       </c>
       <c r="U11" t="n">
-        <v>0.186</v>
+        <v>0.0272</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.493300000000001</v>
+        <v>-4.751099999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.791699999999999</v>
+        <v>-3.3577</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7017</v>
+        <v>-1.3934</v>
       </c>
       <c r="G12" t="n">
-        <v>-15.8946</v>
+        <v>-15.8696</v>
       </c>
       <c r="H12" t="n">
-        <v>-15.8946</v>
+        <v>-15.8695</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0001000000000002318</v>
+        <v>-9.999999999975306e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>6.537100000000001</v>
+        <v>6.343400000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.7643</v>
+        <v>-3.8714</v>
       </c>
       <c r="L12" t="n">
-        <v>10.3016</v>
+        <v>10.215</v>
       </c>
       <c r="M12" t="n">
-        <v>-22.4318</v>
+        <v>-22.213</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.1302</v>
+        <v>-11.9981</v>
       </c>
       <c r="O12" t="n">
-        <v>-10.3015</v>
+        <v>-10.2149</v>
       </c>
       <c r="P12" t="n">
-        <v>5.671</v>
+        <v>5.691000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-19.2809</v>
+        <v>-19.3487</v>
       </c>
       <c r="R12" t="n">
-        <v>24.9517</v>
+        <v>25.0394</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.714300000000001</v>
+        <v>-4.993899999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.3249</v>
+        <v>-2.581</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.3895</v>
+        <v>-2.4128</v>
       </c>
       <c r="V12" t="n">
-        <v>10.4446</v>
+        <v>10.4215</v>
       </c>
       <c r="W12" t="n">
-        <v>12.2765</v>
+        <v>12.2282</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.832</v>
+        <v>-1.8069</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.605499999999999</v>
+        <v>7.4802</v>
       </c>
       <c r="E13" t="n">
-        <v>4.9186</v>
+        <v>3.8079</v>
       </c>
       <c r="F13" t="n">
-        <v>3.6869</v>
+        <v>3.6723</v>
       </c>
       <c r="G13" t="n">
-        <v>5.1199</v>
+        <v>5.1164</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4561</v>
+        <v>4.4411</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6637999999999999</v>
+        <v>0.6753</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8442</v>
+        <v>4.8102</v>
       </c>
       <c r="K13" t="n">
-        <v>3.986</v>
+        <v>3.9537</v>
       </c>
       <c r="L13" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2757</v>
+        <v>0.3062</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S13" t="n">
-        <v>3.0281</v>
+        <v>1.9117</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6998</v>
+        <v>0.6429</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3283</v>
+        <v>1.2688</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.4498</v>
+        <v>-0.4584</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6429</v>
+        <v>0.6311</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.058</v>
+        <v>6.3298</v>
       </c>
       <c r="E14" t="n">
-        <v>2.9812</v>
+        <v>3.1622</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0768</v>
+        <v>3.1676</v>
       </c>
       <c r="G14" t="n">
-        <v>4.0036</v>
+        <v>3.9954</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7487</v>
+        <v>1.7572</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2549</v>
+        <v>2.2381</v>
       </c>
       <c r="J14" t="n">
-        <v>5.4683</v>
+        <v>5.422</v>
       </c>
       <c r="K14" t="n">
-        <v>1.1531</v>
+        <v>1.1409</v>
       </c>
       <c r="L14" t="n">
-        <v>4.3152</v>
+        <v>4.2811</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.4647</v>
+        <v>-1.4266</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5956</v>
+        <v>0.6163999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.0603</v>
+        <v>-2.043</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R14" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2397</v>
+        <v>1.5134</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0061</v>
+        <v>0.2457</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2336</v>
+        <v>1.2677</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.2249</v>
+        <v>-0.2292</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2342</v>
+        <v>4.6828</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3031</v>
+        <v>1.8039</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9312</v>
+        <v>2.8789</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3776</v>
+        <v>0.3763</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5873</v>
+        <v>2.5823</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.2097</v>
+        <v>-2.206</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2274</v>
+        <v>0.1992</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6136</v>
+        <v>1.5923</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.3861</v>
+        <v>-1.3931</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1502</v>
+        <v>0.1771</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9737</v>
+        <v>0.99</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9488</v>
+        <v>2.9592</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9078</v>
+        <v>1.3473</v>
       </c>
       <c r="T15" t="n">
-        <v>0.983</v>
+        <v>0.5152</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9248</v>
+        <v>0.832</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0194</v>
+        <v>2.9428</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8919</v>
+        <v>3.515</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.5722</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9957</v>
+        <v>3.9834</v>
       </c>
       <c r="H16" t="n">
-        <v>2.1805</v>
+        <v>2.169</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8152</v>
+        <v>1.8143</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3606</v>
+        <v>4.3397</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8977</v>
+        <v>1.8821</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4629</v>
+        <v>2.4576</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3649</v>
+        <v>-0.3563</v>
       </c>
       <c r="N16" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7307</v>
+        <v>0.6619</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6654</v>
+        <v>0.3134</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0653</v>
+        <v>0.3485</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SALVO</t>
+          <t>K. ROBERTSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4883</v>
+        <v>0.8204</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0346</v>
+        <v>-1.2902</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4537</v>
+        <v>2.1106</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1919</v>
+        <v>1.3758</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1919</v>
+        <v>1.7931</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.4173</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0346</v>
+        <v>1.9158</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0346</v>
+        <v>1.3058</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1573</v>
+        <v>-0.54</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1573</v>
+        <v>0.4873</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-1.0273</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>3.1868</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0696</v>
+        <v>0.6039</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>0.0507</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0696</v>
+        <v>0.5532</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. ROBERTSON</t>
+          <t>M. SALVO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.401</v>
+        <v>0.6082</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9352</v>
+        <v>0.1529</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5342</v>
+        <v>0.4553</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3965</v>
+        <v>0.1924</v>
       </c>
       <c r="H18" t="n">
-        <v>1.8097</v>
+        <v>0.1924</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4132</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9659</v>
+        <v>0.0345</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3396</v>
+        <v>0.0345</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6263</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5693</v>
+        <v>0.1579</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4701</v>
+        <v>0.1579</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.0395</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.1757</v>
+        <v>0.2276</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6388</v>
+        <v>0.1881</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6593</v>
+        <v>0.1184</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0206</v>
+        <v>0.0697</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6147</v>
+        <v>-1.0817</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1067</v>
+        <v>0.1248</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5081</v>
+        <v>-1.2065</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3737</v>
+        <v>-1.3673</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1343</v>
+        <v>-0.1295</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2395</v>
+        <v>-1.2378</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0839</v>
+        <v>0.0785</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0866</v>
+        <v>0.0862</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0027</v>
+        <v>-0.0077</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4576</v>
+        <v>-1.4458</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2368</v>
+        <v>-1.2301</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0556</v>
+        <v>0.4645</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1905</v>
+        <v>0.0463</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1349</v>
+        <v>0.4182</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0249</v>
+        <v>-1.4294</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.9039</v>
+        <v>-1.3389</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.121</v>
+        <v>-0.0905</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2216</v>
+        <v>0.2256</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1516</v>
+        <v>-0.1467</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3732</v>
+        <v>0.3724</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8282</v>
+        <v>1.8133</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3708</v>
+        <v>-0.376</v>
       </c>
       <c r="L20" t="n">
-        <v>2.199</v>
+        <v>2.1893</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.6066</v>
+        <v>-1.5877</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2072</v>
+        <v>0.8002</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3297</v>
+        <v>0.2622</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.538</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4997</v>
+        <v>-2.2203</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9345</v>
+        <v>-1.9586</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5652</v>
+        <v>-0.2616</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5974</v>
+        <v>0.6008</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0289</v>
+        <v>-0.0233</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6264</v>
+        <v>0.624</v>
       </c>
       <c r="J21" t="n">
-        <v>1.4978</v>
+        <v>1.4886</v>
       </c>
       <c r="K21" t="n">
-        <v>0.381</v>
+        <v>0.3792</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9003</v>
+        <v>-0.8879</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4099</v>
+        <v>-0.4025</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0556</v>
+        <v>0.2276</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1905</v>
+        <v>-0.1906</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1349</v>
+        <v>0.4182</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W21" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.5512</v>
+        <v>-2.9817</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.84</v>
+        <v>-2.5098</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.7113</v>
+        <v>-0.4719</v>
       </c>
       <c r="G22" t="n">
-        <v>2.7832</v>
+        <v>2.7823</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9004</v>
+        <v>2.8953</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="J22" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9568</v>
+        <v>1.9478</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="N22" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1172</v>
+        <v>-0.113</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.359</v>
+        <v>0.2148</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2601</v>
+        <v>0.095</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0989</v>
+        <v>0.1198</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8204</v>
+        <v>-7.0781</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7074</v>
+        <v>-4.0758</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.113</v>
+        <v>-3.0023</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4192</v>
+        <v>-1.4114</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3347</v>
+        <v>0.3387</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.7539</v>
+        <v>-1.7501</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1639</v>
+        <v>0.1634</v>
       </c>
       <c r="K23" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L23" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5831</v>
+        <v>-1.5749</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8658</v>
+        <v>-1.8618</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6403</v>
+        <v>0.382</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6654</v>
+        <v>0.3134</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0251</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.493499999999998</v>
+        <v>8.073000000000004</v>
       </c>
       <c r="E24" t="n">
-        <v>1.701699999999999</v>
+        <v>1.393400000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>4.791700000000001</v>
+        <v>6.6797</v>
       </c>
       <c r="G24" t="n">
-        <v>15.8945</v>
+        <v>15.8697</v>
       </c>
       <c r="H24" t="n">
-        <v>15.8945</v>
+        <v>15.8696</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.220446049250313e-16</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="J24" t="n">
-        <v>22.43160000000001</v>
+        <v>22.213</v>
       </c>
       <c r="K24" t="n">
-        <v>12.1302</v>
+        <v>11.9982</v>
       </c>
       <c r="L24" t="n">
-        <v>10.3017</v>
+        <v>10.2147</v>
       </c>
       <c r="M24" t="n">
-        <v>-6.536899999999999</v>
+        <v>-6.343500000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>3.7644</v>
+        <v>3.8715</v>
       </c>
       <c r="O24" t="n">
-        <v>-10.3016</v>
+        <v>-10.2148</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.671000000000001</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q24" t="n">
-        <v>-24.9517</v>
+        <v>-25.0395</v>
       </c>
       <c r="R24" t="n">
-        <v>19.2807</v>
+        <v>19.3485</v>
       </c>
       <c r="S24" t="n">
-        <v>6.714399999999999</v>
+        <v>8.3154</v>
       </c>
       <c r="T24" t="n">
-        <v>2.3896</v>
+        <v>2.4126</v>
       </c>
       <c r="U24" t="n">
-        <v>4.3248</v>
+        <v>5.902699999999999</v>
       </c>
       <c r="V24" t="n">
-        <v>-10.4446</v>
+        <v>-10.4213</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8321</v>
+        <v>1.807</v>
       </c>
       <c r="X24" t="n">
-        <v>-12.2768</v>
+        <v>-12.2283</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104631_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104631_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-1.8069</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104631_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-12.2283</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
